--- a/115-1社團_多元智能課程名單.xlsx
+++ b/115-1社團_多元智能課程名單.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuhaoyu/Documents/115學年相關/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\163.16.121.157\115學年度\03學輔處\01學輔主任\07社團與多元智能課程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C6982C1-B5EC-C446-AE13-1C890E431D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ADD71B-4BE1-401D-BF93-2064DFC4EAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="620" windowWidth="27600" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="135">
   <si>
     <t>名稱</t>
   </si>
@@ -509,6 +512,10 @@
   </si>
   <si>
     <t>池家勝</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>柯旼祁</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -728,7 +735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -800,6 +807,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -809,14 +819,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1238,251 +1248,251 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="27.796875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" customWidth="1"/>
-    <col min="3" max="3" width="19.796875" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" customWidth="1"/>
-    <col min="5" max="5" width="19.796875" customWidth="1"/>
-    <col min="6" max="6" width="8.796875" customWidth="1"/>
-    <col min="7" max="7" width="19.796875" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" customWidth="1"/>
-    <col min="9" max="9" width="19.796875" customWidth="1"/>
-    <col min="10" max="10" width="8.796875" customWidth="1"/>
-    <col min="11" max="11" width="19.796875" customWidth="1"/>
-    <col min="12" max="12" width="8.796875" customWidth="1"/>
-    <col min="13" max="13" width="19.796875" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" customWidth="1"/>
-    <col min="15" max="15" width="19.796875" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" customWidth="1"/>
-    <col min="17" max="17" width="19.796875" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.85546875" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.5" customHeight="1">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25" t="s">
+      <c r="I1" s="26"/>
+      <c r="J1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="40" t="s">
+      <c r="M1" s="26"/>
+      <c r="N1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40" t="s">
+      <c r="O1" s="41"/>
+      <c r="P1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="40"/>
+      <c r="Q1" s="41"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="26"/>
+      <c r="D2" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="G2" s="26"/>
+      <c r="H2" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="26"/>
+      <c r="J2" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25" t="s">
+      <c r="K2" s="26"/>
+      <c r="L2" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25" t="s">
+      <c r="M2" s="26"/>
+      <c r="N2" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="25" t="s">
+      <c r="O2" s="41"/>
+      <c r="P2" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="40"/>
+      <c r="Q2" s="41"/>
     </row>
     <row r="3" spans="1:17" ht="57.75" customHeight="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
     </row>
     <row r="4" spans="1:17" ht="119.25" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="43" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="43" t="s">
+      <c r="G4" s="40"/>
+      <c r="H4" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="44" t="s">
+      <c r="I4" s="40"/>
+      <c r="J4" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="44" t="s">
+      <c r="K4" s="46"/>
+      <c r="L4" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="45"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="29"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="30"/>
     </row>
     <row r="5" spans="1:17" ht="146.25" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38" t="s">
+      <c r="C5" s="38"/>
+      <c r="D5" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="36" t="s">
+      <c r="E5" s="40"/>
+      <c r="F5" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38" t="s">
+      <c r="G5" s="38"/>
+      <c r="H5" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="38" t="s">
+      <c r="I5" s="40"/>
+      <c r="J5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="38" t="s">
+      <c r="K5" s="40"/>
+      <c r="L5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="39"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="32"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="33"/>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25" t="s">
+      <c r="C6" s="26"/>
+      <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25" t="s">
+      <c r="E6" s="26"/>
+      <c r="F6" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="26"/>
+      <c r="H6" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25" t="s">
+      <c r="I6" s="26"/>
+      <c r="J6" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25" t="s">
+      <c r="K6" s="26"/>
+      <c r="L6" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="35"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="36"/>
     </row>
     <row r="7" spans="1:17" ht="91.5" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="25" t="s">
+      <c r="I7" s="43"/>
+      <c r="J7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="25"/>
-      <c r="N7" s="40" t="s">
+      <c r="M7" s="26"/>
+      <c r="N7" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40" t="s">
+      <c r="O7" s="41"/>
+      <c r="P7" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="40"/>
-    </row>
-    <row r="8" spans="1:17" ht="23">
+      <c r="Q7" s="41"/>
+    </row>
+    <row r="8" spans="1:17" ht="21">
       <c r="A8" s="19" t="s">
         <v>15</v>
       </c>
@@ -1694,7 +1704,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="23">
+    <row r="12" spans="1:17" ht="21">
       <c r="A12" s="3">
         <v>4</v>
       </c>
@@ -1747,7 +1757,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="23">
+    <row r="13" spans="1:17" ht="21">
       <c r="A13" s="3">
         <v>5</v>
       </c>
@@ -1800,7 +1810,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="23">
+    <row r="14" spans="1:17" ht="21">
       <c r="A14" s="3">
         <v>6</v>
       </c>
@@ -1906,7 +1916,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="23">
+    <row r="16" spans="1:17" ht="21">
       <c r="A16" s="3">
         <v>8</v>
       </c>
@@ -1919,13 +1929,13 @@
       <c r="D16" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="25" t="s">
         <v>106</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="25" t="s">
         <v>131</v>
       </c>
       <c r="H16" s="14" t="s">
@@ -1951,11 +1961,11 @@
       <c r="P16" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="22" t="s">
+      <c r="Q16" s="25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="23">
+    <row r="17" spans="1:17" ht="21">
       <c r="A17" s="3">
         <v>9</v>
       </c>
@@ -1966,9 +1976,9 @@
         <v>18</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="E17" s="22"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="14" t="s">
         <v>76</v>
       </c>
@@ -1996,7 +2006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23">
+    <row r="18" spans="1:17" ht="21">
       <c r="A18" s="3">
         <v>10</v>
       </c>
@@ -2026,7 +2036,7 @@
         <v>80</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -2037,7 +2047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23">
+    <row r="19" spans="1:17" ht="21">
       <c r="A19" s="3">
         <v>11</v>
       </c>
@@ -2057,13 +2067,17 @@
       <c r="I19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="J19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="L19" s="3" t="s">
         <v>80</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
@@ -2074,7 +2088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="23">
+    <row r="20" spans="1:17" ht="21">
       <c r="A20" s="3">
         <v>12</v>
       </c>
@@ -2097,10 +2111,10 @@
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
@@ -2111,7 +2125,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="23">
+    <row r="21" spans="1:17" ht="21">
       <c r="A21" s="3">
         <v>13</v>
       </c>
@@ -2134,10 +2148,10 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>55</v>
+        <v>80</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
@@ -2148,7 +2162,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="23">
+    <row r="22" spans="1:17" ht="21">
       <c r="A22" s="3">
         <v>14</v>
       </c>
@@ -2170,12 +2184,8 @@
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
-      <c r="L22" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="13" t="s">
@@ -2185,7 +2195,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="23">
+    <row r="23" spans="1:17" ht="21">
       <c r="A23" s="3">
         <v>15</v>
       </c>
@@ -2218,7 +2228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="23">
+    <row r="24" spans="1:17" ht="21">
       <c r="A24" s="3">
         <v>16</v>
       </c>
@@ -2251,7 +2261,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="23">
+    <row r="25" spans="1:17" ht="21">
       <c r="A25" s="3">
         <v>17</v>
       </c>
@@ -2284,7 +2294,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="23">
+    <row r="26" spans="1:17" ht="21">
       <c r="A26" s="3">
         <v>18</v>
       </c>
@@ -2317,7 +2327,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="23">
+    <row r="27" spans="1:17" ht="21">
       <c r="A27" s="3">
         <v>19</v>
       </c>
@@ -2350,7 +2360,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="23">
+    <row r="28" spans="1:17" ht="21">
       <c r="A28" s="1">
         <v>20</v>
       </c>
@@ -2380,10 +2390,10 @@
         <v>76</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="23">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="21">
       <c r="A29" s="1">
         <v>21</v>
       </c>
@@ -2412,7 +2422,7 @@
       <c r="P29" s="14"/>
       <c r="Q29" s="12"/>
     </row>
-    <row r="30" spans="1:17" ht="23">
+    <row r="30" spans="1:17" ht="21">
       <c r="A30" s="1">
         <v>22</v>
       </c>
@@ -2441,7 +2451,7 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
     </row>
-    <row r="31" spans="1:17" ht="23">
+    <row r="31" spans="1:17" ht="21">
       <c r="A31" s="1">
         <v>23</v>
       </c>
@@ -2470,7 +2480,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:17" ht="23">
+    <row r="32" spans="1:17" ht="21">
       <c r="A32" s="1">
         <v>24</v>
       </c>
@@ -2499,7 +2509,7 @@
       <c r="P32" s="17"/>
       <c r="Q32" s="17"/>
     </row>
-    <row r="33" spans="1:17" ht="23">
+    <row r="33" spans="1:17" ht="21">
       <c r="A33" s="1">
         <v>25</v>
       </c>
@@ -2528,7 +2538,7 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
     </row>
-    <row r="34" spans="1:17" ht="23">
+    <row r="34" spans="1:17" ht="21">
       <c r="A34" s="1">
         <v>26</v>
       </c>
@@ -2553,7 +2563,7 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
     </row>
-    <row r="35" spans="1:17" ht="23">
+    <row r="35" spans="1:17" ht="21">
       <c r="A35" s="1">
         <v>27</v>
       </c>
@@ -2578,7 +2588,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
     </row>
-    <row r="36" spans="1:17" ht="23">
+    <row r="36" spans="1:17" ht="21">
       <c r="A36" s="1">
         <v>28</v>
       </c>
@@ -2603,7 +2613,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:17" ht="23">
+    <row r="37" spans="1:17" ht="21">
       <c r="A37" s="1">
         <v>29</v>
       </c>
@@ -2628,7 +2638,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:17" ht="22">
+    <row r="38" spans="1:17" ht="21">
       <c r="A38" s="1">
         <v>30</v>
       </c>
@@ -2649,80 +2659,80 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:17" ht="23">
+    <row r="39" spans="1:17" ht="21">
       <c r="A39" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="26">
         <v>25</v>
       </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="40">
+      <c r="C39" s="26"/>
+      <c r="D39" s="41">
         <v>8</v>
       </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="25">
+      <c r="E39" s="41"/>
+      <c r="F39" s="26">
         <v>8</v>
       </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25">
+      <c r="G39" s="26"/>
+      <c r="H39" s="26">
         <v>29</v>
       </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="25">
-        <v>10</v>
-      </c>
-      <c r="K39" s="25"/>
-      <c r="L39" s="40">
-        <v>14</v>
-      </c>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40">
+      <c r="I39" s="41"/>
+      <c r="J39" s="26">
+        <v>11</v>
+      </c>
+      <c r="K39" s="26"/>
+      <c r="L39" s="41">
+        <v>13</v>
+      </c>
+      <c r="M39" s="41"/>
+      <c r="N39" s="41">
         <v>7</v>
       </c>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41" t="s">
+      <c r="O39" s="41"/>
+      <c r="P39" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="Q39" s="41"/>
-    </row>
-    <row r="40" spans="1:17" ht="16">
+      <c r="Q39" s="42"/>
+    </row>
+    <row r="40" spans="1:17">
       <c r="O40" s="5"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:17" ht="16">
+    <row r="41" spans="1:17">
       <c r="O41" s="5"/>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:17" ht="16">
+    <row r="42" spans="1:17">
       <c r="O42" s="5"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:17" ht="16">
+    <row r="43" spans="1:17">
       <c r="O43" s="5"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:17" ht="16">
+    <row r="44" spans="1:17">
       <c r="O44" s="5"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:17" ht="16">
+    <row r="45" spans="1:17">
       <c r="O45" s="5"/>
       <c r="Q45" s="5"/>
     </row>
-    <row r="46" spans="1:17" ht="16">
+    <row r="46" spans="1:17">
       <c r="O46" s="5"/>
       <c r="Q46" s="5"/>
     </row>
-    <row r="47" spans="1:17" ht="16">
+    <row r="47" spans="1:17">
       <c r="O47" s="5"/>
       <c r="Q47" s="5"/>
     </row>
-    <row r="48" spans="1:17" ht="16">
+    <row r="48" spans="1:17">
       <c r="O48" s="5"/>
       <c r="Q48" s="5"/>
     </row>
-    <row r="49" spans="15:17" ht="16">
+    <row r="49" spans="15:17">
       <c r="O49" s="5"/>
       <c r="Q49" s="5"/>
     </row>
@@ -2783,7 +2793,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="58" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="67" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>